--- a/审核导出/silicone_led_uv_spray_审核.xlsx
+++ b/审核导出/silicone_led_uv_spray_审核.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>濕樣：乳白色 / 干樣：透明</t>
+          <t>濕樣：乳白色 / 幹樣：透明</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -825,12 +825,12 @@
       </c>
       <c r="AA1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="AB1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="AC1" s="3" t="inlineStr">
